--- a/artfynd/A 24356-2024 artfynd.xlsx
+++ b/artfynd/A 24356-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676099</v>
+        <v>118676098</v>
       </c>
       <c r="B2" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676101</v>
+        <v>118676099</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
+        <v>78220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508102</v>
+        <v>508223</v>
       </c>
       <c r="R4" t="n">
-        <v>6837805</v>
+        <v>6837837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676098</v>
+        <v>118676101</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>79565</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508223</v>
+        <v>508102</v>
       </c>
       <c r="R5" t="n">
-        <v>6837837</v>
+        <v>6837805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24356-2024 artfynd.xlsx
+++ b/artfynd/A 24356-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676098</v>
+        <v>118676100</v>
       </c>
       <c r="B2" t="n">
-        <v>78221</v>
+        <v>78484</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508223</v>
+        <v>508142</v>
       </c>
       <c r="R2" t="n">
-        <v>6837837</v>
+        <v>6837798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676100</v>
+        <v>118676101</v>
       </c>
       <c r="B3" t="n">
-        <v>78484</v>
+        <v>79565</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508142</v>
+        <v>508102</v>
       </c>
       <c r="R3" t="n">
-        <v>6837798</v>
+        <v>6837805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676101</v>
+        <v>118676098</v>
       </c>
       <c r="B5" t="n">
-        <v>79565</v>
+        <v>78221</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508102</v>
+        <v>508223</v>
       </c>
       <c r="R5" t="n">
-        <v>6837805</v>
+        <v>6837837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24356-2024 artfynd.xlsx
+++ b/artfynd/A 24356-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676100</v>
+        <v>118676099</v>
       </c>
       <c r="B2" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508142</v>
+        <v>508223</v>
       </c>
       <c r="R2" t="n">
-        <v>6837798</v>
+        <v>6837837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676101</v>
+        <v>118676098</v>
       </c>
       <c r="B3" t="n">
-        <v>79565</v>
+        <v>78228</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508102</v>
+        <v>508223</v>
       </c>
       <c r="R3" t="n">
-        <v>6837805</v>
+        <v>6837837</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676099</v>
+        <v>118676100</v>
       </c>
       <c r="B4" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508223</v>
+        <v>508142</v>
       </c>
       <c r="R4" t="n">
-        <v>6837837</v>
+        <v>6837798</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676098</v>
+        <v>118676101</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>79572</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508223</v>
+        <v>508102</v>
       </c>
       <c r="R5" t="n">
-        <v>6837837</v>
+        <v>6837805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 24356-2024 artfynd.xlsx
+++ b/artfynd/A 24356-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118676099</v>
+        <v>118676100</v>
       </c>
       <c r="B2" t="n">
-        <v>78227</v>
+        <v>78491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508223</v>
+        <v>508142</v>
       </c>
       <c r="R2" t="n">
-        <v>6837837</v>
+        <v>6837798</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118676098</v>
+        <v>118676099</v>
       </c>
       <c r="B3" t="n">
-        <v>78228</v>
+        <v>78227</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118676100</v>
+        <v>118676098</v>
       </c>
       <c r="B4" t="n">
-        <v>78491</v>
+        <v>78228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -941,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508142</v>
+        <v>508223</v>
       </c>
       <c r="R4" t="n">
-        <v>6837798</v>
+        <v>6837837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
